--- a/Programs/A3ASM/GT_Aufgabe_Woche_3_Speicher.xlsx
+++ b/Programs/A3ASM/GT_Aufgabe_Woche_3_Speicher.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/narekavetisyan/Downloads/Praktikum/Woche 03/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/narekavetisyan/GT Repo/ITS-BRD-VSC/Programs/A3ASM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36264D15-F84F-204C-8C79-EA9D8421041E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE57C64-6756-9841-A193-DAB3759BFD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{2F3BCCD5-4B63-4AFE-B627-FCE26E36F91B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t xml:space="preserve">In B6 und in A8 soll die die Startadresse von VariableA stehen. </t>
   </si>
@@ -119,10 +119,22 @@
     <t>0x2000002c</t>
   </si>
   <si>
-    <t>0x2000004c</t>
-  </si>
-  <si>
-    <t>0x2000006c</t>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>9D</t>
+  </si>
+  <si>
+    <t>4E</t>
+  </si>
+  <si>
+    <t>0x2000001c</t>
+  </si>
+  <si>
+    <t>0x2000003c</t>
+  </si>
+  <si>
+    <t>CC</t>
   </si>
 </sst>
 </file>
@@ -130,7 +142,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="00"/>
+    <numFmt numFmtId="164" formatCode="00"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -154,7 +166,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -224,6 +236,66 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF898BA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF9B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABFFD8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB2FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62FF78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7193FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF2E66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF56FFF0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -255,34 +327,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF56FFF0"/>
+      <color rgb="FFFF2E66"/>
+      <color rgb="FF7193FF"/>
+      <color rgb="FF62FF78"/>
+      <color rgb="FFFFB2FF"/>
+      <color rgb="FFABFFD8"/>
+      <color rgb="FFFFFF9B"/>
+      <color rgb="FF75FFFF"/>
+      <color rgb="FFF898BA"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -732,127 +828,127 @@
     </row>
     <row r="9" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="19">
-        <v>0</v>
-      </c>
-      <c r="C9" s="19">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="B9" s="18">
+        <v>27</v>
+      </c>
+      <c r="C9" s="18">
+        <v>0</v>
+      </c>
+      <c r="D9" s="18">
+        <v>45</v>
+      </c>
+      <c r="E9" s="19">
+        <v>0</v>
       </c>
       <c r="F9" s="14">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G9" s="14">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H9" s="14">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I9" s="15">
+        <v>12</v>
+      </c>
+      <c r="J9" s="16">
+        <v>86</v>
+      </c>
+      <c r="K9" s="16">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="16">
-        <v>0</v>
-      </c>
-      <c r="K9" s="16">
-        <v>0</v>
-      </c>
-      <c r="L9" s="16">
-        <v>0</v>
-      </c>
-      <c r="M9" s="17">
-        <v>45</v>
-      </c>
-      <c r="N9" s="18">
-        <v>41</v>
-      </c>
-      <c r="O9" s="18">
-        <v>42</v>
-      </c>
-      <c r="P9" s="18">
-        <v>61</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>62</v>
+      <c r="M9" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="20">
+        <v>0</v>
+      </c>
+      <c r="O9" s="20">
+        <v>0</v>
+      </c>
+      <c r="P9" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="20" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="21">
+        <v>0</v>
+      </c>
+      <c r="C10" s="21">
+        <v>0</v>
+      </c>
+      <c r="D10" s="21">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0</v>
+      </c>
+      <c r="H10" s="16">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16">
         <v>27</v>
       </c>
-      <c r="B10" s="5">
-        <v>0</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>0</v>
+      <c r="J10" s="22">
+        <v>0</v>
+      </c>
+      <c r="K10" s="22">
+        <v>0</v>
+      </c>
+      <c r="L10" s="22">
+        <v>0</v>
+      </c>
+      <c r="M10" s="22">
+        <v>45</v>
+      </c>
+      <c r="N10" s="23">
+        <v>41</v>
+      </c>
+      <c r="O10" s="24">
+        <v>42</v>
+      </c>
+      <c r="P10" s="25">
+        <v>61</v>
+      </c>
+      <c r="Q10" s="26">
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
+        <v>31</v>
+      </c>
+      <c r="B11" s="27">
+        <v>30</v>
+      </c>
+      <c r="C11" s="28">
+        <v>31</v>
+      </c>
+      <c r="D11" s="29">
+        <v>32</v>
+      </c>
+      <c r="E11" s="30">
+        <v>33</v>
+      </c>
+      <c r="F11" s="31">
         <v>0</v>
       </c>
       <c r="G11" s="5">
@@ -895,15 +991,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e961261f-4e0e-4566-a231-1dc83598657b" xsi:nil="true"/>
-    <TaxCatchAll xmlns="b33a431a-7215-4989-bff9-879665c68a7c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101005D65133E7A0CF9449DD091B941F90EF8" ma:contentTypeVersion="10" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e2d6616748466e5dc409f60b6ea371d8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e961261f-4e0e-4566-a231-1dc83598657b" xmlns:ns3="b33a431a-7215-4989-bff9-879665c68a7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5db98142609301bb6b695eb65a27a0c9" ns2:_="" ns3:_="">
     <xsd:import namespace="e961261f-4e0e-4566-a231-1dc83598657b"/>
@@ -1090,6 +1177,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e961261f-4e0e-4566-a231-1dc83598657b" xsi:nil="true"/>
+    <TaxCatchAll xmlns="b33a431a-7215-4989-bff9-879665c68a7c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1100,17 +1196,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11A288FA-0013-4976-BB46-C34CB2235849}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e961261f-4e0e-4566-a231-1dc83598657b"/>
-    <ds:schemaRef ds:uri="b33a431a-7215-4989-bff9-879665c68a7c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A87FB59E-9EEE-402D-8B53-E7499378C5DA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1129,6 +1214,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11A288FA-0013-4976-BB46-C34CB2235849}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e961261f-4e0e-4566-a231-1dc83598657b"/>
+    <ds:schemaRef ds:uri="b33a431a-7215-4989-bff9-879665c68a7c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD416654-AA39-493D-8922-853FE1EB435E}">
   <ds:schemaRefs>
